--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00836B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00836B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEDD1FF7-07FD-426A-BAFD-57F955239861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25AFDA0A-3A67-497C-824B-EC46D166E73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{B461BE9C-5C49-4EF8-8A73-F6E183BF7D45}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{1C2B976D-A245-4EB6-927F-206F6B333141}"/>
   </bookViews>
   <sheets>
     <sheet name="00836B-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1556,25 +1556,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A33DB4D-F9C7-4155-9817-43A3BCE62A43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257BAEFF-63D1-4B98-865D-189E03888E55}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1728,7 +1728,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2020</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2019</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>25</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39" t="s">
         <v>71</v>
       </c>
